--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.7</v>
+        <v>30.34</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.34</v>
+        <v>31.098</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.098</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.5</v>
+        <v>29.74</v>
       </c>
     </row>
     <row r="5">

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -482,7 +482,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>26.26539943955155</v>
+        <v>28.16411959022745</v>
       </c>
     </row>
     <row r="6">
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24.80672021365856</v>
+        <v>27.97125379811839</v>
       </c>
     </row>
     <row r="9">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3162500</v>
+        <v>148289.149433564</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50</v>
+        <v>2.344492481163067</v>
       </c>
     </row>
   </sheetData>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>24.61276613177428</v>
+        <v>28.61485208115096</v>
       </c>
       <c r="F11" t="n">
-        <v>19.46183215844877</v>
+        <v>22.6263657429086</v>
       </c>
     </row>
     <row r="12">
@@ -1006,7 +1006,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>24.80672021365856</v>
+        <v>27.97125379811839</v>
       </c>
     </row>
     <row r="13">
@@ -1034,9 +1034,9 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
@@ -1080,19 +1080,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17.20531404192144</v>
+        <v>18.51495692976764</v>
       </c>
       <c r="C2" t="n">
-        <v>21.7353567407365</v>
+        <v>23.1637231738013</v>
       </c>
       <c r="D2" t="n">
-        <v>26.26539943955155</v>
+        <v>27.81248941783496</v>
       </c>
       <c r="E2" t="n">
-        <v>30.79544213836661</v>
+        <v>32.46125566186863</v>
       </c>
       <c r="F2" t="n">
-        <v>35.32548483718165</v>
+        <v>37.11002190590228</v>
       </c>
     </row>
     <row r="3">
@@ -1102,19 +1102,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17.20531404192144</v>
+        <v>18.69077201596388</v>
       </c>
       <c r="C3" t="n">
-        <v>21.7353567407365</v>
+        <v>23.33953825999754</v>
       </c>
       <c r="D3" t="n">
-        <v>26.26539943955155</v>
+        <v>27.98830450403121</v>
       </c>
       <c r="E3" t="n">
-        <v>30.79544213836661</v>
+        <v>32.63707074806487</v>
       </c>
       <c r="F3" t="n">
-        <v>35.32548483718165</v>
+        <v>37.28583699209852</v>
       </c>
     </row>
     <row r="4">
@@ -1124,19 +1124,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17.20531404192144</v>
+        <v>18.86658710216012</v>
       </c>
       <c r="C4" t="n">
-        <v>21.7353567407365</v>
+        <v>23.51535334619378</v>
       </c>
       <c r="D4" t="n">
-        <v>26.26539943955155</v>
+        <v>28.16411959022745</v>
       </c>
       <c r="E4" t="n">
-        <v>30.79544213836661</v>
+        <v>32.81288583426111</v>
       </c>
       <c r="F4" t="n">
-        <v>35.32548483718165</v>
+        <v>37.46165207829476</v>
       </c>
     </row>
     <row r="5">
@@ -1146,19 +1146,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17.20531404192144</v>
+        <v>19.04240218835636</v>
       </c>
       <c r="C5" t="n">
-        <v>21.7353567407365</v>
+        <v>23.69116843239002</v>
       </c>
       <c r="D5" t="n">
-        <v>26.26539943955155</v>
+        <v>28.33993467642369</v>
       </c>
       <c r="E5" t="n">
-        <v>30.79544213836661</v>
+        <v>32.98870092045735</v>
       </c>
       <c r="F5" t="n">
-        <v>35.32548483718165</v>
+        <v>37.63746716449101</v>
       </c>
     </row>
     <row r="6">
@@ -1168,19 +1168,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17.20531404192144</v>
+        <v>19.2182172745526</v>
       </c>
       <c r="C6" t="n">
-        <v>21.7353567407365</v>
+        <v>23.86698351858627</v>
       </c>
       <c r="D6" t="n">
-        <v>26.26539943955155</v>
+        <v>28.51574976261993</v>
       </c>
       <c r="E6" t="n">
-        <v>30.79544213836661</v>
+        <v>33.16451600665359</v>
       </c>
       <c r="F6" t="n">
-        <v>35.32548483718165</v>
+        <v>37.81328225068724</v>
       </c>
     </row>
   </sheetData>
@@ -1218,7 +1218,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>29.47</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="3">
@@ -1226,7 +1226,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>30.07</v>
+        <v>28.59</v>
       </c>
     </row>
     <row r="4">
@@ -1234,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>30.27</v>
+        <v>28.61</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.74</v>
+        <v>29.48</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>148289.149433564</v>
+        <v>134258.7834771031</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.344492481163067</v>
+        <v>2.122668513471986</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -472,7 +472,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.48</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="5">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>134258.7834771031</v>
+        <v>124005.823739689</v>
       </c>
     </row>
     <row r="16">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.122668513471986</v>
+        <v>1.96056638323619</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -12,7 +12,6 @@
     <sheet name="DivStrip" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Payout" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Warnings" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1240,35 +1239,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Data validation warnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>spot TCE VLCC: $388,300/day is 9.7x the 10-yr mean ($40,000) — unsustainable as a level. Confirm it is a genuine cycle spike (not a unit/source error) and do not anchor valuation to it.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.29</v>
+        <v>28.06</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>124005.823739689</v>
+        <v>57631.40017643145</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.96056638323619</v>
+        <v>0.9111683822360703</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.06</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>57631.40017643145</v>
+        <v>87850.64992880904</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.9111683822360703</v>
+        <v>1.388943081878404</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>28.62</v>
+        <v>29.29</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87850.64992880904</v>
+        <v>124005.823739689</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.388943081878404</v>
+        <v>1.96056638323619</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.29</v>
+        <v>29.17</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>124005.823739689</v>
+        <v>117530.2702213225</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.96056638323619</v>
+        <v>1.858186090455692</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.17</v>
+        <v>30.01</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>117530.2702213225</v>
+        <v>162859.1448498891</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.858186090455692</v>
+        <v>2.574848139919195</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.01</v>
+        <v>30.14</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>162859.1448498891</v>
+        <v>169874.3278281192</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.574848139919195</v>
+        <v>2.685760123764731</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.14</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>169874.3278281192</v>
+        <v>206029.5016389997</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.685760123764731</v>
+        <v>3.257383425122526</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.81</v>
+        <v>30.67</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>206029.5016389997</v>
+        <v>198474.6892009053</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.257383425122526</v>
+        <v>3.137939750211941</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.67</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>198474.6892009053</v>
+        <v>192538.7651424026</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.137939750211941</v>
+        <v>3.044091148496483</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.56</v>
+        <v>30.85</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>192538.7651424026</v>
+        <v>208188.0194784552</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.044091148496483</v>
+        <v>3.291510189382691</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.85</v>
+        <v>31.155</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>208188.0194784552</v>
+        <v>224646.7180043036</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.291510189382691</v>
+        <v>3.55172676686646</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.155</v>
+        <v>30.84</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>224646.7180043036</v>
+        <v>207648.3900185913</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.55172676686646</v>
+        <v>3.282978498317649</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.84</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>207648.3900185913</v>
+        <v>135338.0423968307</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.282978498317649</v>
+        <v>2.139731895602067</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29.5</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>135338.0423968307</v>
+        <v>205489.8721791358</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.139731895602067</v>
+        <v>3.248851734057483</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-Q1</t>
+          <t>2026-Q2</t>
         </is>
       </c>
     </row>
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30.8</v>
+        <v>31.93</v>
       </c>
     </row>
     <row r="5">
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>28.16411959022745</v>
+        <v>27.01212328920753</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28.45341827839103</v>
+        <v>27.2220062953049</v>
       </c>
     </row>
     <row r="8">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.97125379811839</v>
+        <v>26.87220128514261</v>
       </c>
     </row>
     <row r="9">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>205489.8721791358</v>
+        <v>328633.1153122117</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.248851734057483</v>
+        <v>5.195780479244453</v>
       </c>
     </row>
   </sheetData>
@@ -633,7 +633,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2915</v>
+        <v>2869.5</v>
       </c>
     </row>
     <row r="3">
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>389.068</v>
+        <v>397.382</v>
       </c>
     </row>
     <row r="4">
@@ -653,7 +653,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>56</v>
+        <v>-0.711</v>
       </c>
     </row>
     <row r="5">
@@ -663,7 +663,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-1820.955</v>
+        <v>-1793.668</v>
       </c>
     </row>
     <row r="6">
@@ -702,7 +702,7 @@
         <v/>
       </c>
       <c r="B9" t="n">
-        <v>1539.113</v>
+        <v>1472.503</v>
       </c>
     </row>
     <row r="10">
@@ -722,7 +722,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28.45341827839103</v>
+        <v>27.2220062953049</v>
       </c>
     </row>
     <row r="12">
@@ -732,7 +732,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28.45341827839103</v>
+        <v>27.2220062953049</v>
       </c>
     </row>
     <row r="13">
@@ -763,7 +763,7 @@
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28.61485208115096</v>
+        <v>27.22491498539462</v>
       </c>
       <c r="F11" t="n">
-        <v>22.6263657429086</v>
+        <v>21.52731322993282</v>
       </c>
     </row>
     <row r="12">
@@ -1005,7 +1005,7 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>27.97125379811839</v>
+        <v>26.87220128514261</v>
       </c>
     </row>
     <row r="13">
@@ -1036,8 +1036,8 @@
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1079,19 +1079,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18.51495692976764</v>
+        <v>17.52510896665093</v>
       </c>
       <c r="C2" t="n">
-        <v>23.1637231738013</v>
+        <v>22.09280104173299</v>
       </c>
       <c r="D2" t="n">
-        <v>27.81248941783496</v>
+        <v>26.66049311681504</v>
       </c>
       <c r="E2" t="n">
-        <v>32.46125566186863</v>
+        <v>31.22818519189711</v>
       </c>
       <c r="F2" t="n">
-        <v>37.11002190590228</v>
+        <v>35.79587726697916</v>
       </c>
     </row>
     <row r="3">
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18.69077201596388</v>
+        <v>17.70092405284717</v>
       </c>
       <c r="C3" t="n">
-        <v>23.33953825999754</v>
+        <v>22.26861612792923</v>
       </c>
       <c r="D3" t="n">
-        <v>27.98830450403121</v>
+        <v>26.83630820301128</v>
       </c>
       <c r="E3" t="n">
-        <v>32.63707074806487</v>
+        <v>31.40400027809335</v>
       </c>
       <c r="F3" t="n">
-        <v>37.28583699209852</v>
+        <v>35.9716923531754</v>
       </c>
     </row>
     <row r="4">
@@ -1123,19 +1123,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18.86658710216012</v>
+        <v>17.87673913904341</v>
       </c>
       <c r="C4" t="n">
-        <v>23.51535334619378</v>
+        <v>22.44443121412547</v>
       </c>
       <c r="D4" t="n">
-        <v>28.16411959022745</v>
+        <v>27.01212328920753</v>
       </c>
       <c r="E4" t="n">
-        <v>32.81288583426111</v>
+        <v>31.57981536428959</v>
       </c>
       <c r="F4" t="n">
-        <v>37.46165207829476</v>
+        <v>36.14750743937164</v>
       </c>
     </row>
     <row r="5">
@@ -1145,19 +1145,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19.04240218835636</v>
+        <v>18.05255422523965</v>
       </c>
       <c r="C5" t="n">
-        <v>23.69116843239002</v>
+        <v>22.62024630032171</v>
       </c>
       <c r="D5" t="n">
-        <v>28.33993467642369</v>
+        <v>27.18793837540377</v>
       </c>
       <c r="E5" t="n">
-        <v>32.98870092045735</v>
+        <v>31.75563045048583</v>
       </c>
       <c r="F5" t="n">
-        <v>37.63746716449101</v>
+        <v>36.32332252556789</v>
       </c>
     </row>
     <row r="6">
@@ -1167,19 +1167,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2182172745526</v>
+        <v>18.2283693114359</v>
       </c>
       <c r="C6" t="n">
-        <v>23.86698351858627</v>
+        <v>22.79606138651796</v>
       </c>
       <c r="D6" t="n">
-        <v>28.51574976261993</v>
+        <v>27.36375346160001</v>
       </c>
       <c r="E6" t="n">
-        <v>33.16451600665359</v>
+        <v>31.93144553668207</v>
       </c>
       <c r="F6" t="n">
-        <v>37.81328225068724</v>
+        <v>36.49913761176413</v>
       </c>
     </row>
   </sheetData>
@@ -1217,7 +1217,7 @@
         <v>0.8</v>
       </c>
       <c r="B2" t="n">
-        <v>28.52</v>
+        <v>27.37</v>
       </c>
     </row>
     <row r="3">
@@ -1225,7 +1225,7 @@
         <v>0.95</v>
       </c>
       <c r="B3" t="n">
-        <v>28.59</v>
+        <v>27.44</v>
       </c>
     </row>
     <row r="4">
@@ -1233,7 +1233,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="n">
-        <v>28.61</v>
+        <v>27.46</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/flng_fv_report.xlsx
+++ b/outputs/flng_fv_report.xlsx
@@ -471,7 +471,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>31.93</v>
+        <v>31.48</v>
       </c>
     </row>
     <row r="5">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>328633.1153122117</v>
+        <v>304349.7896183369</v>
       </c>
     </row>
     <row r="16">
@@ -593,7 +593,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5.195780479244453</v>
+        <v>4.81185438131758</v>
       </c>
     </row>
   </sheetData>
